--- a/artfynd/A 14093-2022 artfynd.xlsx
+++ b/artfynd/A 14093-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14093-2022 artfynd.xlsx
+++ b/artfynd/A 14093-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100335640</v>
+        <v>100404680</v>
       </c>
       <c r="B2" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tierp, Upl</t>
+          <t>Nybron SO, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659926.8928836639</v>
+        <v>659962</v>
       </c>
       <c r="R2" t="n">
-        <v>6694385.729997403</v>
+        <v>6694467</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,6 +768,26 @@
           <t>Björksumpskog</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Svamp, fruktkropp mm</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fungi, fruit bodies, etc. # Fomes fomentarius</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -798,19 +799,18 @@
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100404680</v>
+        <v>100335640</v>
       </c>
       <c r="B3" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,42 +818,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybron SO, Upl</t>
+          <t>Tierp, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659962.0265766785</v>
+        <v>659927</v>
       </c>
       <c r="R3" t="n">
-        <v>6694467.052805133</v>
+        <v>6694386</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +881,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,26 +914,6 @@
           <t>Björksumpskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Svamp, fruktkropp mm</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Fungi, fruit bodies, etc. # Fomes fomentarius</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -941,9 +925,473 @@
           <t>Johan Lilja</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>60289141</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Udde i Finnsjöns nordöstra del, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>659881</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6694214</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström, Felicia Alriksson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>60289092</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Udde i Finnsjöns nordöstra del, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>659881</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6694214</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström, Felicia Alriksson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>60289075</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Udde i Finnsjöns nordöstra del, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>659881</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6694214</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Jörgen Sjöström, Felicia Alriksson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>60289040</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Udde i Finnsjöns nordöstra del, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>659881</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6694214</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-06-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Felicia Alriksson, Jörgen Sjöström, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 14093-2022 artfynd.xlsx
+++ b/artfynd/A 14093-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100335640</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60289141</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60289092</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60289075</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1285,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60289040</t>
         </is>
       </c>
     </row>
@@ -1394,8 +1424,21 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100404680</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>